--- a/Wordle_Duel_Sprint_Backlog.xlsx
+++ b/Wordle_Duel_Sprint_Backlog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/81ab7734a6a69e1a/Documents/Cna/Fall 2025/CP3490 Software Engineering/Wordle_Duel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2E01E2D-A6CF-40DF-AF76-CB4D12BD72FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{C2E01E2D-A6CF-40DF-AF76-CB4D12BD72FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{608431F9-FF95-43B0-A871-1FFFD7DCA4F9}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="9780" windowWidth="31590" windowHeight="18225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint Backlog" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="35">
   <si>
     <t>Sprint Goal</t>
   </si>
@@ -110,6 +110,21 @@
   </si>
   <si>
     <t>As a user, I want to log in securely.</t>
+  </si>
+  <si>
+    <t>Tyler</t>
+  </si>
+  <si>
+    <t>Seth</t>
+  </si>
+  <si>
+    <t>Tyler/Seth</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>Cancelled</t>
   </si>
 </sst>
 </file>
@@ -186,6 +201,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -480,8 +499,8 @@
     <col min="2" max="2" width="101.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="64" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -514,11 +533,11 @@
       <c r="C2" t="s">
         <v>8</v>
       </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
       <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -531,8 +550,11 @@
       <c r="C3" t="s">
         <v>12</v>
       </c>
+      <c r="D3" t="s">
+        <v>31</v>
+      </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F3" t="s">
         <v>10</v>
@@ -548,8 +570,11 @@
       <c r="C4" t="s">
         <v>14</v>
       </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F4" t="s">
         <v>10</v>
@@ -565,8 +590,11 @@
       <c r="C5" t="s">
         <v>17</v>
       </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s">
         <v>10</v>
@@ -582,8 +610,11 @@
       <c r="C6" t="s">
         <v>19</v>
       </c>
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
         <v>10</v>
@@ -599,6 +630,9 @@
       <c r="C7" t="s">
         <v>21</v>
       </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
@@ -616,8 +650,11 @@
       <c r="C8" t="s">
         <v>23</v>
       </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="F8" t="s">
         <v>10</v>
@@ -633,8 +670,11 @@
       <c r="C9" t="s">
         <v>25</v>
       </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
         <v>10</v>
@@ -649,6 +689,9 @@
       </c>
       <c r="C10" t="s">
         <v>28</v>
+      </c>
+      <c r="D10" t="s">
+        <v>32</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
